--- a/src/attributions/attributions_ig_traj_58.xlsx
+++ b/src/attributions/attributions_ig_traj_58.xlsx
@@ -2140,25 +2140,25 @@
         <v>0</v>
       </c>
       <c r="B4" t="n">
-        <v>0.06151757844986793</v>
+        <v>0.08074070645783528</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.006264158863841146</v>
+        <v>-0.01425476642604581</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0445071252859037</v>
+        <v>-0.05275548700857847</v>
       </c>
       <c r="G4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
@@ -2167,34 +2167,34 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0.02952676859720245</v>
+        <v>0.0902202686158675</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.007383776338731849</v>
+        <v>-0.01429349899041657</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.04318197903740162</v>
+        <v>-0.03931753522447304</v>
       </c>
       <c r="P4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>1.733296892002573e-12</v>
+        <v>-1.237324954457808e-11</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2203,52 +2203,52 @@
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.002093183420500053</v>
+        <v>0.01050889044559535</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.003112954095465442</v>
+        <v>0.003771720337797531</v>
       </c>
       <c r="Y4" t="n">
         <v>-0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB4" t="n">
         <v>-0</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.0073387158379619</v>
+        <v>-0.04030971772187414</v>
       </c>
       <c r="AD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02209590716269821</v>
+        <v>-0.04549174230697696</v>
       </c>
       <c r="AG4" t="n">
-        <v>-0.00291711895694557</v>
+        <v>-0.04175434548220389</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI4" t="n">
         <v>-0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.01523302455542294</v>
+        <v>0.01254225253383503</v>
       </c>
       <c r="AM4" t="n">
         <v>0</v>
@@ -2257,13 +2257,13 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>-0.009521183454342734</v>
+        <v>-0.01651317992360488</v>
       </c>
       <c r="AP4" t="n">
-        <v>-0.01872128587364284</v>
+        <v>-0.02708894584626004</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR4" t="n">
         <v>0</v>
@@ -2272,22 +2272,22 @@
         <v>0</v>
       </c>
       <c r="AT4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.08306087811613144</v>
+        <v>0.2436509678659874</v>
       </c>
       <c r="AV4" t="n">
         <v>-0</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AX4" t="n">
-        <v>-0.005351170474668294</v>
+        <v>-0.02993381695501363</v>
       </c>
       <c r="AY4" t="n">
-        <v>-0.06717270008509434</v>
+        <v>-0.02419879973128964</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2296,67 +2296,67 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC4" t="n">
         <v>0</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.01035627935441267</v>
+        <v>-0.004353789169818595</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF4" t="n">
         <v>0</v>
       </c>
       <c r="BG4" t="n">
-        <v>-0.008377532814982136</v>
+        <v>-0.01781954461187711</v>
       </c>
       <c r="BH4" t="n">
-        <v>-1.643224659816602e-11</v>
+        <v>-3.31687051179469e-11</v>
       </c>
       <c r="BI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02711185467707717</v>
+        <v>0.02911439010601298</v>
       </c>
       <c r="BN4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO4" t="n">
         <v>-0</v>
       </c>
       <c r="BP4" t="n">
-        <v>-0.004939344756505712</v>
+        <v>0.0650032021097115</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.01273985849455776</v>
+        <v>0.05316702334951012</v>
       </c>
       <c r="BR4" t="n">
         <v>-0</v>
       </c>
       <c r="BS4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BU4" t="n">
         <v>-0</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.04347970316528633</v>
+        <v>0.1089284412088458</v>
       </c>
       <c r="BW4" t="n">
         <v>0</v>
@@ -2365,10 +2365,10 @@
         <v>0</v>
       </c>
       <c r="BY4" t="n">
-        <v>-0.01274046112942279</v>
+        <v>-0.04087147737323993</v>
       </c>
       <c r="BZ4" t="n">
-        <v>-0.006681476161402359</v>
+        <v>-0.06238548407994839</v>
       </c>
       <c r="CA4" t="n">
         <v>-0</v>
@@ -2377,106 +2377,106 @@
         <v>0</v>
       </c>
       <c r="CC4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD4" t="n">
         <v>-0</v>
       </c>
       <c r="CE4" t="n">
-        <v>-0.01518195695743078</v>
+        <v>-0.03549880311053992</v>
       </c>
       <c r="CF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG4" t="n">
         <v>-0</v>
       </c>
       <c r="CH4" t="n">
-        <v>-0.007119276117770749</v>
+        <v>0.002114294757617955</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.03389061873772829</v>
+        <v>0.04866248634355699</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK4" t="n">
         <v>0</v>
       </c>
       <c r="CL4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.004220800188567688</v>
+        <v>-0.08424969275457019</v>
       </c>
       <c r="CO4" t="n">
         <v>-0</v>
       </c>
       <c r="CP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.009086548436788825</v>
+        <v>0.06417590805808943</v>
       </c>
       <c r="CR4" t="n">
-        <v>-0.01255948373539565</v>
+        <v>0.03347381138118877</v>
       </c>
       <c r="CS4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT4" t="n">
         <v>-0</v>
       </c>
       <c r="CU4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW4" t="n">
-        <v>-0.01236100356947819</v>
+        <v>-0.04052029845630595</v>
       </c>
       <c r="CX4" t="n">
         <v>0</v>
       </c>
       <c r="CY4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ4" t="n">
-        <v>-0.007465075812480916</v>
+        <v>-0.007886858225092525</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.03655684439617373</v>
+        <v>0.04498656502866487</v>
       </c>
       <c r="DB4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF4" t="n">
-        <v>-0.01124859271921664</v>
+        <v>-0.01100378502799528</v>
       </c>
       <c r="DG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.0173012481113183</v>
+        <v>-0.04407492237014596</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.04316577628929945</v>
+        <v>-0.004659852138120286</v>
       </c>
       <c r="DK4" t="n">
         <v>0</v>
@@ -2485,28 +2485,28 @@
         <v>-0</v>
       </c>
       <c r="DM4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN4" t="n">
         <v>-0</v>
       </c>
       <c r="DO4" t="n">
-        <v>-0.005530905548973567</v>
+        <v>-0.02493543268655047</v>
       </c>
       <c r="DP4" t="n">
         <v>0</v>
       </c>
       <c r="DQ4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.008196264897568292</v>
+        <v>0.03972086615811191</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.002454789933630153</v>
+        <v>0.06724198652098723</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
@@ -2518,19 +2518,19 @@
         <v>-0</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001494225231264139</v>
+        <v>-0.008877618092370922</v>
       </c>
       <c r="DY4" t="n">
         <v>0</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA4" t="n">
-        <v>-0.005776400151957955</v>
+        <v>0.0006894617154233257</v>
       </c>
       <c r="EB4" t="n">
-        <v>-0.02607926624246887</v>
+        <v>-0.05570706157647633</v>
       </c>
       <c r="EC4" t="n">
         <v>-0</v>
@@ -2539,106 +2539,106 @@
         <v>-0</v>
       </c>
       <c r="EE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG4" t="n">
-        <v>-0.006582875530561338</v>
+        <v>-0.03624326769858137</v>
       </c>
       <c r="EH4" t="n">
         <v>-0</v>
       </c>
       <c r="EI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ4" t="n">
-        <v>-0.002317480305515998</v>
+        <v>-0.0348691070242432</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.02051884007528583</v>
+        <v>0.01520929904914784</v>
       </c>
       <c r="EL4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP4" t="n">
-        <v>-0.003724687617102447</v>
+        <v>0.01698801311083191</v>
       </c>
       <c r="EQ4" t="n">
         <v>-0</v>
       </c>
       <c r="ER4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES4" t="n">
-        <v>-0.0135205805171917</v>
+        <v>-0.04179530270818906</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.04151813803139272</v>
+        <v>0.03419344478142301</v>
       </c>
       <c r="EU4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY4" t="n">
-        <v>-0.01223853225873275</v>
+        <v>-0.04424126972532501</v>
       </c>
       <c r="EZ4" t="n">
         <v>-0</v>
       </c>
       <c r="FA4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB4" t="n">
-        <v>-0.005739481573729847</v>
+        <v>-0.01271925019711849</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.03401302283240527</v>
+        <v>0.03636035010822335</v>
       </c>
       <c r="FD4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE4" t="n">
         <v>0</v>
       </c>
       <c r="FF4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG4" t="n">
         <v>0</v>
       </c>
       <c r="FH4" t="n">
-        <v>-0.01547752889232037</v>
+        <v>-0.07470291865568748</v>
       </c>
       <c r="FI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ4" t="n">
         <v>-0</v>
       </c>
       <c r="FK4" t="n">
-        <v>-0.01457021959409249</v>
+        <v>0.01952976987465782</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.006430573276815056</v>
+        <v>-0.02750758671756595</v>
       </c>
       <c r="FM4" t="n">
         <v>0</v>
@@ -2647,25 +2647,25 @@
         <v>-0</v>
       </c>
       <c r="FO4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.0009822097580128742</v>
+        <v>0.03875159081902758</v>
       </c>
       <c r="FR4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS4" t="n">
         <v>-0</v>
       </c>
       <c r="FT4" t="n">
-        <v>-0.01756091438898378</v>
+        <v>0.007116673746703249</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.0215000442937</v>
+        <v>0.02956628614248619</v>
       </c>
       <c r="FV4" t="n">
         <v>-0</v>
@@ -2674,13 +2674,13 @@
         <v>-0</v>
       </c>
       <c r="FX4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ4" t="n">
-        <v>-0.01768101668098829</v>
+        <v>-0.006733082729187843</v>
       </c>
       <c r="GA4" t="n">
         <v>0</v>
@@ -2692,39 +2692,39 @@
         <v>0</v>
       </c>
       <c r="GD4" t="n">
-        <v>-0.013311210740497</v>
+        <v>0.02327044403457647</v>
       </c>
       <c r="GE4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF4" t="n">
         <v>0</v>
       </c>
       <c r="GG4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B5" t="n">
-        <v>0.1724234544045913</v>
+        <v>0.1577162892521851</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.07585239999227658</v>
+        <v>-0.09532991945398947</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.08628636090390075</v>
+        <v>-0.007325326703450527</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H5" t="n">
         <v>-0</v>
@@ -2733,28 +2733,28 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.08276756519281532</v>
+        <v>0.1094722509412944</v>
       </c>
       <c r="L5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.06777166865891619</v>
+        <v>-0.1026385524696196</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.07939755403872839</v>
+        <v>-0.0227288585795739</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -2763,16 +2763,16 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.00640846014281817</v>
+        <v>0.005978811986451487</v>
       </c>
       <c r="U5" t="n">
         <v>-0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.104230440547656e-11</v>
+        <v>-1.271382676852486e-11</v>
       </c>
       <c r="W5" t="n">
-        <v>2.86822030297845e-11</v>
+        <v>-8.752865555328308e-12</v>
       </c>
       <c r="X5" t="n">
         <v>-0</v>
@@ -2781,7 +2781,7 @@
         <v>-0</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
@@ -2790,76 +2790,76 @@
         <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.04196935418672475</v>
+        <v>-0.01289145134730696</v>
       </c>
       <c r="AD5" t="n">
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.06041925534435127</v>
+        <v>-0.07064042151094752</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1046666930498403</v>
+        <v>-0.01793439882472891</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.03737524314159328</v>
+        <v>0.07395848623294674</v>
       </c>
       <c r="AM5" t="n">
         <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.02613559976629062</v>
+        <v>-0.02777313735422035</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.08211185786169932</v>
+        <v>0.06090877522788795</v>
       </c>
       <c r="AP5" t="n">
         <v>0</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0.3961347801296478</v>
+        <v>0.2190530952383018</v>
       </c>
       <c r="AV5" t="n">
         <v>-0</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.1147286101690576</v>
+        <v>-0.07810938832582084</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.2097702142974795</v>
+        <v>-0.1385575981411658</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA5" t="n">
         <v>0</v>
@@ -2868,52 +2868,52 @@
         <v>-0</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.0005919995656516177</v>
+        <v>0.003119751035129318</v>
       </c>
       <c r="BE5" t="n">
         <v>0</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.1700562626355458</v>
+        <v>-0.03330876083156497</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.03619513607100312</v>
+        <v>-0.004854685882623512</v>
       </c>
       <c r="BH5" t="n">
         <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK5" t="n">
         <v>0</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.1561279831450206</v>
+        <v>-0.004150702234647999</v>
       </c>
       <c r="BN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.01226765475414163</v>
+        <v>0.04144831339053135</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.1879084532707371</v>
+        <v>0.07420220097957567</v>
       </c>
       <c r="BQ5" t="n">
         <v>-0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS5" t="n">
         <v>-0</v>
@@ -2925,43 +2925,43 @@
         <v>-0</v>
       </c>
       <c r="BV5" t="n">
-        <v>0.1872711880369845</v>
+        <v>0.150572183957068</v>
       </c>
       <c r="BW5" t="n">
         <v>0</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.01394230555374526</v>
+        <v>0.0259967443464297</v>
       </c>
       <c r="BY5" t="n">
-        <v>0.01965042601331922</v>
+        <v>-0.0252264375963038</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB5" t="n">
         <v>0</v>
       </c>
       <c r="CC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.05634890581955826</v>
+        <v>-0.08696475574600919</v>
       </c>
       <c r="CF5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG5" t="n">
-        <v>0.008891811238783527</v>
+        <v>0.07079602656275026</v>
       </c>
       <c r="CH5" t="n">
-        <v>0.002489767116518908</v>
+        <v>0.005637408061634264</v>
       </c>
       <c r="CI5" t="n">
         <v>-0</v>
@@ -2970,7 +2970,7 @@
         <v>-0</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL5" t="n">
         <v>-0</v>
@@ -2979,19 +2979,19 @@
         <v>0</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.0551040252096518</v>
+        <v>-0.08381154420255447</v>
       </c>
       <c r="CO5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.1107635822338896</v>
+        <v>0.07681060091847591</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.224658681164599</v>
+        <v>0.08474084324684859</v>
       </c>
       <c r="CR5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS5" t="n">
         <v>-0</v>
@@ -3000,22 +3000,22 @@
         <v>-0</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW5" t="n">
-        <v>-0.03933904007676879</v>
+        <v>-0.09460757708308691</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY5" t="n">
-        <v>0.01530863054278753</v>
+        <v>0.07747139201670816</v>
       </c>
       <c r="CZ5" t="n">
-        <v>0.0270513350794167</v>
+        <v>0.01184158684928662</v>
       </c>
       <c r="DA5" t="n">
         <v>0</v>
@@ -3024,28 +3024,28 @@
         <v>0</v>
       </c>
       <c r="DC5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD5" t="n">
         <v>0</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.002279848997276466</v>
+        <v>-0.00484371459088736</v>
       </c>
       <c r="DG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH5" t="n">
-        <v>0.03541979791980274</v>
+        <v>0.02042431627679113</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.01897097177757372</v>
+        <v>-0.05299512299128802</v>
       </c>
       <c r="DJ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK5" t="n">
         <v>-0</v>
@@ -3057,82 +3057,82 @@
         <v>0</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.1070766190701942</v>
+        <v>-0.06652742063617774</v>
       </c>
       <c r="DP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ5" t="n">
-        <v>0.04944942023359825</v>
+        <v>0.03408696622724983</v>
       </c>
       <c r="DR5" t="n">
-        <v>0.03509041488514254</v>
+        <v>-0.04794035875624564</v>
       </c>
       <c r="DS5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU5" t="n">
         <v>-0</v>
       </c>
       <c r="DV5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW5" t="n">
         <v>-0</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.01415344296257563</v>
+        <v>0.03531762496729696</v>
       </c>
       <c r="DY5" t="n">
         <v>0</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.04044638023015785</v>
+        <v>0.06018968747666519</v>
       </c>
       <c r="EA5" t="n">
-        <v>0.02250758742305195</v>
+        <v>0.01441418273942781</v>
       </c>
       <c r="EB5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC5" t="n">
         <v>-0</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE5" t="n">
         <v>-0</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.04616437675588373</v>
+        <v>-0.06161526843893915</v>
       </c>
       <c r="EH5" t="n">
         <v>-0</v>
       </c>
       <c r="EI5" t="n">
-        <v>0.02113408988202038</v>
+        <v>0.05593336325580018</v>
       </c>
       <c r="EJ5" t="n">
-        <v>0.07239941636019709</v>
+        <v>0.03053910703348361</v>
       </c>
       <c r="EK5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL5" t="n">
         <v>-0</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN5" t="n">
         <v>-0</v>
@@ -3141,100 +3141,100 @@
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.03536021030333159</v>
+        <v>-0.02205241692460423</v>
       </c>
       <c r="EQ5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.03061718235734359</v>
+        <v>0.01637695062875208</v>
       </c>
       <c r="ES5" t="n">
-        <v>0.02132986232451508</v>
+        <v>-0.008607128092698074</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW5" t="n">
         <v>-0</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.04176446853170641</v>
+        <v>-0.1055004356097296</v>
       </c>
       <c r="EZ5" t="n">
         <v>-0</v>
       </c>
       <c r="FA5" t="n">
-        <v>0.01708796097808401</v>
+        <v>0.09040230581619847</v>
       </c>
       <c r="FB5" t="n">
-        <v>0.0295468318297748</v>
+        <v>0.0002411554251909449</v>
       </c>
       <c r="FC5" t="n">
         <v>-0</v>
       </c>
       <c r="FD5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF5" t="n">
         <v>-0</v>
       </c>
       <c r="FG5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH5" t="n">
-        <v>0.0532115217766757</v>
+        <v>-0.06909044644684886</v>
       </c>
       <c r="FI5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ5" t="n">
-        <v>-0.04457929445408893</v>
+        <v>-0.05004066604492894</v>
       </c>
       <c r="FK5" t="n">
-        <v>0.001003151270714691</v>
+        <v>0.04725148958865371</v>
       </c>
       <c r="FL5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM5" t="n">
         <v>0</v>
       </c>
       <c r="FN5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO5" t="n">
         <v>0</v>
       </c>
       <c r="FP5" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ5" t="n">
-        <v>-0.08506089638680379</v>
+        <v>0.05095585433569393</v>
       </c>
       <c r="FR5" t="n">
         <v>0</v>
       </c>
       <c r="FS5" t="n">
-        <v>0.03513431638929641</v>
+        <v>0.1163155975342863</v>
       </c>
       <c r="FT5" t="n">
-        <v>0.0942754447541501</v>
+        <v>-0.06836351378958402</v>
       </c>
       <c r="FU5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV5" t="n">
         <v>-0</v>
@@ -3243,25 +3243,25 @@
         <v>0</v>
       </c>
       <c r="FX5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ5" t="n">
-        <v>-0.02215988441782742</v>
+        <v>-0.06554939642602851</v>
       </c>
       <c r="GA5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB5" t="n">
-        <v>-0.0564526179491303</v>
+        <v>0.03218354206574535</v>
       </c>
       <c r="GC5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD5" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE5" t="n">
         <v>-0</v>
@@ -3275,25 +3275,25 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.02369615752043212</v>
+        <v>0.0295532450767958</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.01627939737406781</v>
+        <v>0.0100920484468917</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.004861798200636073</v>
+        <v>-0.008754853996634846</v>
       </c>
       <c r="G6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -3302,25 +3302,25 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.007015752417675417</v>
+        <v>0.03733811481186305</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M6" t="n">
         <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01610259310161196</v>
+        <v>0.004406645728533654</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0056548100515296</v>
+        <v>-0.00744034696460636</v>
       </c>
       <c r="P6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -3329,55 +3329,55 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0005794118159106669</v>
+        <v>9.455796642248405e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0005545282283040809</v>
+        <v>-0.002538346649907532</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.003252332958346637</v>
+        <v>6.957756491802542e-05</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z6" t="n">
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB6" t="n">
         <v>-0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.01392863404066435</v>
+        <v>-0.01210804842916034</v>
       </c>
       <c r="AD6" t="n">
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.01335270792779916</v>
+        <v>-0.04393320577953892</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.0003421293342581613</v>
+        <v>-0.007526831496206367</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
         <v>-0</v>
@@ -3386,22 +3386,22 @@
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.007034579062149699</v>
+        <v>0.009373506888972545</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN6" t="n">
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0199828843011322</v>
+        <v>-0.007565674662119559</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.005640688431233748</v>
+        <v>-0.02281570995170337</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR6" t="n">
         <v>-0</v>
@@ -3410,25 +3410,25 @@
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.05138058695196019</v>
+        <v>0.08684760144643285</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW6" t="n">
         <v>0</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.01549815152147675</v>
+        <v>-0.01758149563100185</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.008857825392231899</v>
+        <v>-0.01614143671170352</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
         <v>0</v>
@@ -3437,25 +3437,25 @@
         <v>-0</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.003023672749568873</v>
+        <v>-0.00364330523381663</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.009932914374643749</v>
+        <v>-0.006795390552289293</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.00281184794865558</v>
+        <v>0.006155119179891146</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ6" t="n">
         <v>0</v>
@@ -3464,37 +3464,37 @@
         <v>0</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0309470636961331</v>
+        <v>0.01632376784823191</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO6" t="n">
         <v>-0</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.01131711544429801</v>
+        <v>0.03366746770605313</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.01196695574700179</v>
+        <v>0.0318241570283565</v>
       </c>
       <c r="BR6" t="n">
         <v>-0</v>
       </c>
       <c r="BS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT6" t="n">
         <v>0</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.02079202753567077</v>
+        <v>0.04461318934716949</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
@@ -3503,13 +3503,13 @@
         <v>0</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.01290329386841188</v>
+        <v>-0.0009397732834029622</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.01965766889991798</v>
+        <v>-0.03296094492913813</v>
       </c>
       <c r="CA6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB6" t="n">
         <v>0</v>
@@ -3521,76 +3521,76 @@
         <v>-0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.0008294423140172999</v>
+        <v>-0.009817216255052247</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0006909565746196228</v>
+        <v>-0.001546454273901052</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.006648213298335437</v>
+        <v>0.02078531052002896</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL6" t="n">
         <v>-0</v>
       </c>
       <c r="CM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.001135198681124018</v>
+        <v>-0.02944251533864623</v>
       </c>
       <c r="CO6" t="n">
         <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.001136449819293926</v>
+        <v>0.0377967133615922</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.01369979139185658</v>
+        <v>0.02422129484124626</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT6" t="n">
         <v>-0</v>
       </c>
       <c r="CU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV6" t="n">
         <v>0</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.003981112681505907</v>
+        <v>-0.01199444805577324</v>
       </c>
       <c r="CX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.002017675676713774</v>
+        <v>-0.002021455582453595</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.007695103823367752</v>
+        <v>0.01844576453083205</v>
       </c>
       <c r="DB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC6" t="n">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.0003365456325160317</v>
+        <v>-0.01359480455562907</v>
       </c>
       <c r="DG6" t="n">
         <v>-0</v>
@@ -3611,10 +3611,10 @@
         <v>-0</v>
       </c>
       <c r="DI6" t="n">
-        <v>-2.079773386770612e-05</v>
+        <v>-0.0007852707214175702</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.01022506835645479</v>
+        <v>-0.003564761498474447</v>
       </c>
       <c r="DK6" t="n">
         <v>0</v>
@@ -3623,40 +3623,40 @@
         <v>-0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
         <v>-0</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.003914361427102905</v>
+        <v>-0.01018410506230133</v>
       </c>
       <c r="DP6" t="n">
         <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR6" t="n">
-        <v>0.01135395809992555</v>
+        <v>0.0006735593594563721</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.003826528052192792</v>
+        <v>0.02745291454342741</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>-0</v>
       </c>
       <c r="DW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0125375213875257</v>
+        <v>-0.003026589153323142</v>
       </c>
       <c r="DY6" t="n">
         <v>0</v>
@@ -3665,16 +3665,16 @@
         <v>-0</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.01222243690631695</v>
+        <v>-0.008275105182245305</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.001871343493646625</v>
+        <v>0.02129836915390438</v>
       </c>
       <c r="EC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
         <v>-0</v>
@@ -3683,100 +3683,100 @@
         <v>-0</v>
       </c>
       <c r="EG6" t="n">
-        <v>0.004693803817180612</v>
+        <v>-0.005134390817642579</v>
       </c>
       <c r="EH6" t="n">
         <v>-0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.003640633358725985</v>
+        <v>-0.01784491027122002</v>
       </c>
       <c r="EK6" t="n">
-        <v>0.006007105603693716</v>
+        <v>0.001844608913859064</v>
       </c>
       <c r="EL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
       </c>
       <c r="EO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP6" t="n">
-        <v>0.00339514007595435</v>
+        <v>-0.000299996135472185</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES6" t="n">
-        <v>-0.01263398375015113</v>
+        <v>-0.01123239846407071</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.03481365157147202</v>
+        <v>0.01552569325132594</v>
       </c>
       <c r="EU6" t="n">
         <v>0</v>
       </c>
       <c r="EV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX6" t="n">
         <v>-0</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.00504924438945633</v>
+        <v>-0.01571941009921566</v>
       </c>
       <c r="EZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001538356017054229</v>
+        <v>-0.008001986460583305</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.01024089455617086</v>
+        <v>0.01360971609977919</v>
       </c>
       <c r="FD6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF6" t="n">
         <v>-0</v>
       </c>
       <c r="FG6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.01201858082751567</v>
+        <v>-0.01544483238284711</v>
       </c>
       <c r="FI6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ6" t="n">
         <v>-0</v>
       </c>
       <c r="FK6" t="n">
-        <v>-0.01421241829712526</v>
+        <v>0.01245467692827011</v>
       </c>
       <c r="FL6" t="n">
-        <v>0.02166862852976348</v>
+        <v>0.005330801998594367</v>
       </c>
       <c r="FM6" t="n">
         <v>0</v>
@@ -3785,13 +3785,13 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.00628014013610882</v>
+        <v>0.02141692252941443</v>
       </c>
       <c r="FR6" t="n">
         <v>-0</v>
@@ -3800,10 +3800,10 @@
         <v>-0</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.004434982718726029</v>
+        <v>-0.000221169566046071</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0004231040504699799</v>
+        <v>-0.02687113502723961</v>
       </c>
       <c r="FV6" t="n">
         <v>-0</v>
@@ -3812,31 +3812,31 @@
         <v>-0</v>
       </c>
       <c r="FX6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>-0.01833448044428889</v>
+        <v>0.01265450941629816</v>
       </c>
       <c r="GA6" t="n">
         <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC6" t="n">
         <v>-0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0.006149180742051567</v>
+        <v>0.01453422892901316</v>
       </c>
       <c r="GE6" t="n">
         <v>0</v>
       </c>
       <c r="GF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG6" t="n">
         <v>0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.09621517254716988</v>
+        <v>0.04889564377543429</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,25 +3856,25 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.01085576736940839</v>
+        <v>-0.02426940505321156</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H7" t="n">
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.01014104878374382</v>
+        <v>-0.003416942137320157</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0388667563193091</v>
+        <v>0.05825525362849779</v>
       </c>
       <c r="L7" t="n">
         <v>-0</v>
@@ -3883,7 +3883,7 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.04529113290465307</v>
+        <v>-0.02334213409249779</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -3895,13 +3895,13 @@
         <v>-0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.0117308522379342</v>
+        <v>-0.002688925645060931</v>
       </c>
       <c r="S7" t="n">
         <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.004534038330129311</v>
+        <v>-0.001703185879768387</v>
       </c>
       <c r="U7" t="n">
         <v>-0</v>
@@ -3910,34 +3910,34 @@
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.003099748330083481</v>
+        <v>-0.005452305685902009</v>
       </c>
       <c r="X7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
-        <v>-0.0006520111396533534</v>
+        <v>0.0003717263846565933</v>
       </c>
       <c r="AB7" t="n">
         <v>-0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.02878681174824684</v>
+        <v>-0.01094662895582084</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.02261178963928306</v>
+        <v>-0.01666597569516667</v>
       </c>
       <c r="AG7" t="n">
         <v>0</v>
@@ -3946,16 +3946,16 @@
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004621876704463578</v>
+        <v>-9.343075307596309e-05</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.02806302750136101</v>
+        <v>0.02459558115293833</v>
       </c>
       <c r="AM7" t="n">
         <v>0</v>
@@ -3964,34 +3964,34 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.02444721981608952</v>
+        <v>-0.004618809013163238</v>
       </c>
       <c r="AP7" t="n">
         <v>0</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.01676950234040031</v>
+        <v>-0.00456185646089013</v>
       </c>
       <c r="AT7" t="n">
         <v>-0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.1855775757600771</v>
+        <v>0.0916090055849255</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.06782018533407337</v>
+        <v>-0.01979869798726265</v>
       </c>
       <c r="AY7" t="n">
         <v>0</v>
@@ -4003,13 +4003,13 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.005130822780535725</v>
+        <v>0.01052309571534074</v>
       </c>
       <c r="BC7" t="n">
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.007982531375752814</v>
+        <v>-0.002062623224128486</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,7 +4018,7 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.02747188227152782</v>
+        <v>-0.009956055127338827</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
@@ -4027,16 +4027,16 @@
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.01994699419720076</v>
+        <v>0.01006726762303618</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.01774486949884594</v>
+        <v>0.01294286615362423</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,52 +4045,52 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.07863114093203601</v>
+        <v>0.03571368645246331</v>
       </c>
       <c r="BQ7" t="n">
         <v>-0</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
         <v>-0</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.02587460201374581</v>
+        <v>0.01070587744232982</v>
       </c>
       <c r="BU7" t="n">
         <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0930181696645629</v>
+        <v>0.0524394975945299</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.00913604147311986</v>
+        <v>-0.02262860300470331</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB7" t="n">
         <v>0</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.01344437443301469</v>
+        <v>-0.01599108310776355</v>
       </c>
       <c r="CD7" t="n">
         <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02194169236439666</v>
+        <v>-0.02220241911862478</v>
       </c>
       <c r="CF7" t="n">
         <v>-0</v>
@@ -4099,10 +4099,10 @@
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>-0.002525513441973712</v>
+        <v>0.008978668635175867</v>
       </c>
       <c r="CI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ7" t="n">
         <v>-0</v>
@@ -4111,25 +4111,25 @@
         <v>0</v>
       </c>
       <c r="CL7" t="n">
-        <v>0.02857987568343638</v>
+        <v>0.01089205022285764</v>
       </c>
       <c r="CM7" t="n">
         <v>0</v>
       </c>
       <c r="CN7" t="n">
-        <v>-0.02237040998962355</v>
+        <v>-0.04150270714699356</v>
       </c>
       <c r="CO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP7" t="n">
         <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>-0.02160989721178494</v>
+        <v>0.006734120558606153</v>
       </c>
       <c r="CR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
@@ -4138,13 +4138,13 @@
         <v>-0</v>
       </c>
       <c r="CU7" t="n">
-        <v>-0.004896971275379041</v>
+        <v>0.01615910875953483</v>
       </c>
       <c r="CV7" t="n">
         <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01809293082518872</v>
+        <v>-0.02266758607883661</v>
       </c>
       <c r="CX7" t="n">
         <v>0</v>
@@ -4153,25 +4153,25 @@
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.001696089508389789</v>
+        <v>0.005590486271440402</v>
       </c>
       <c r="DA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.02835947243463679</v>
+        <v>0.01007289504844724</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.07591903459584413</v>
+        <v>-0.01482107214754742</v>
       </c>
       <c r="DG7" t="n">
         <v>-0</v>
@@ -4180,7 +4180,7 @@
         <v>-0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.03432965550359691</v>
+        <v>-0.008485081660211575</v>
       </c>
       <c r="DJ7" t="n">
         <v>-0</v>
@@ -4189,55 +4189,55 @@
         <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.003293180302426062</v>
+        <v>-0.006478680211486309</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.003935862885775828</v>
+        <v>-0.01525866436857871</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>-0.006215503434935499</v>
+        <v>0.008618801520615237</v>
       </c>
       <c r="DS7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU7" t="n">
         <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>-0.001594389817384727</v>
+        <v>-0.02595751545488465</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.0004592089785149597</v>
+        <v>0.01370923436990267</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
         <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>-0.01810560698377254</v>
+        <v>-0.001052066768931015</v>
       </c>
       <c r="EB7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
@@ -4246,40 +4246,40 @@
         <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>-0.01606826355195244</v>
+        <v>-0.006067869811559622</v>
       </c>
       <c r="EF7" t="n">
         <v>0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.002234654409924309</v>
+        <v>-0.0149687123631599</v>
       </c>
       <c r="EH7" t="n">
         <v>0</v>
       </c>
       <c r="EI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.02181410461987696</v>
+        <v>0.001024715967135887</v>
       </c>
       <c r="EK7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM7" t="n">
         <v>0</v>
       </c>
       <c r="EN7" t="n">
-        <v>0.02845928612046047</v>
+        <v>0.004016852941336322</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.03961828092685292</v>
+        <v>-0.004375827176876987</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
@@ -4288,25 +4288,25 @@
         <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.000910224599170139</v>
+        <v>-9.144984042282583e-05</v>
       </c>
       <c r="ET7" t="n">
         <v>-0</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV7" t="n">
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>0.01414485275481801</v>
+        <v>0.006525575741314225</v>
       </c>
       <c r="EX7" t="n">
         <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.02961258701703793</v>
+        <v>-0.02656081272997552</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,7 +4315,7 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.002599939545259947</v>
+        <v>0.002206461406749292</v>
       </c>
       <c r="FC7" t="n">
         <v>-0</v>
@@ -4327,22 +4327,22 @@
         <v>0</v>
       </c>
       <c r="FF7" t="n">
-        <v>0.01806742231322473</v>
+        <v>0.01067292590786453</v>
       </c>
       <c r="FG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02837576683751707</v>
+        <v>-0.01419741572696862</v>
       </c>
       <c r="FI7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>-0.0274073758923272</v>
+        <v>0.006074076455052073</v>
       </c>
       <c r="FL7" t="n">
         <v>0</v>
@@ -4351,16 +4351,16 @@
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.01131448708826654</v>
+        <v>0.03737114900531163</v>
       </c>
       <c r="FP7" t="n">
         <v>-0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>-0.04917304012342708</v>
+        <v>0.01172734122585122</v>
       </c>
       <c r="FR7" t="n">
         <v>-0</v>
@@ -4369,7 +4369,7 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.008170591494498692</v>
+        <v>-0.0170886837401196</v>
       </c>
       <c r="FU7" t="n">
         <v>0</v>
@@ -4381,16 +4381,16 @@
         <v>-0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0002040553276842725</v>
+        <v>0.001608543668238914</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>-0.03805602328597589</v>
+        <v>-0.009086535967404967</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
@@ -4399,16 +4399,16 @@
         <v>0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE7" t="n">
         <v>-0</v>
       </c>
       <c r="GF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>0.02920196601618617</v>
+        <v>0.0002402699512194037</v>
       </c>
     </row>
     <row r="8">
@@ -4985,22 +4985,22 @@
         <v>0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.308837513699337</v>
+        <v>0.1264738399751813</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1589860402525157</v>
+        <v>-0.04402579942121836</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.05896441198662523</v>
+        <v>-0.01702195620431365</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H9" t="n">
         <v>-0</v>
@@ -5009,100 +5009,100 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1738801710880599</v>
+        <v>0.1158273237274006</v>
       </c>
       <c r="L9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.1748480064177955</v>
+        <v>-0.08187430256637043</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.09078821872728558</v>
+        <v>-0.04123078783916164</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P9" t="n">
         <v>-0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.03192809770401349</v>
+        <v>0.01808214466632853</v>
       </c>
       <c r="U9" t="n">
         <v>-0</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.001387649776204901</v>
+        <v>-0.006569023519681754</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.01878444132903621</v>
+        <v>-0.005398066478914896</v>
       </c>
       <c r="X9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.09609342156927538</v>
+        <v>-0.01431688772013636</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.01583361763630926</v>
+        <v>-0.09085848207881611</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.02614210105954132</v>
+        <v>-0.06252947352120714</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>-0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.01201434169659742</v>
+        <v>0.102314559493287</v>
       </c>
       <c r="AM9" t="n">
         <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0.02333848054016761</v>
+        <v>-0.04600328655021037</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.1169364095724832</v>
+        <v>0.06590564845754388</v>
       </c>
       <c r="AP9" t="n">
         <v>0</v>
@@ -5114,25 +5114,25 @@
         <v>-0</v>
       </c>
       <c r="AS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.4865642780238283</v>
+        <v>0.1734274569225736</v>
       </c>
       <c r="AV9" t="n">
         <v>-0</v>
       </c>
       <c r="AW9" t="n">
-        <v>-0.01411881013775301</v>
+        <v>-0.007699553544779159</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.1655598123403939</v>
+        <v>-0.1126125033707952</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -5147,16 +5147,16 @@
         <v>-0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.004597855773339872</v>
+        <v>-0.02133790936322288</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
       </c>
       <c r="BF9" t="n">
-        <v>-0.08634637356778407</v>
+        <v>-0.03844846232581964</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.09473611216678739</v>
+        <v>-0.01957107745286304</v>
       </c>
       <c r="BH9" t="n">
         <v>0</v>
@@ -5165,7 +5165,7 @@
         <v>-0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
         <v>0</v>
@@ -5174,22 +5174,22 @@
         <v>-0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.1774821396635779</v>
+        <v>0.02168485868676777</v>
       </c>
       <c r="BN9" t="n">
         <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.06548650014818584</v>
+        <v>0.02102423224217126</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.1233943477860986</v>
+        <v>0.05978617330457102</v>
       </c>
       <c r="BQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>-0</v>
@@ -5201,22 +5201,22 @@
         <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.2549388721522159</v>
+        <v>0.1614912647460369</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.009772335770081523</v>
+        <v>0.02265691117953537</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.0009088234190569114</v>
+        <v>-0.01937976625635035</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB9" t="n">
         <v>0</v>
@@ -5228,25 +5228,25 @@
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.07264711792594522</v>
+        <v>-0.05885335786136502</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01284544761467159</v>
+        <v>0.05011014435304606</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.01698158723797281</v>
+        <v>0.01941489909776453</v>
       </c>
       <c r="CI9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ9" t="n">
         <v>-0</v>
       </c>
       <c r="CK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL9" t="n">
         <v>-0</v>
@@ -5255,25 +5255,25 @@
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.08005486311620783</v>
+        <v>-0.08481592774511362</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>-0.1510881336018197</v>
+        <v>0.1698109758750273</v>
       </c>
       <c r="CQ9" t="n">
-        <v>-0.1078269145765783</v>
+        <v>0.0777348953339316</v>
       </c>
       <c r="CR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS9" t="n">
         <v>-0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
         <v>-0</v>
@@ -5282,25 +5282,25 @@
         <v>0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.04879397122791831</v>
+        <v>-0.04772236703030728</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.04427389187067311</v>
+        <v>0.05590969922229047</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.003947588426968985</v>
+        <v>0.02723990414582344</v>
       </c>
       <c r="DA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
       </c>
       <c r="DC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD9" t="n">
         <v>0</v>
@@ -5309,19 +5309,19 @@
         <v>-0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.008355738328355745</v>
+        <v>0.0003873227695351287</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.03942212670202858</v>
+        <v>0.002573950380875081</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.02088159297517147</v>
+        <v>-0.05013381794329898</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK9" t="n">
         <v>-0</v>
@@ -5333,19 +5333,19 @@
         <v>0</v>
       </c>
       <c r="DN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.07304922844680363</v>
+        <v>-0.06573895603757868</v>
       </c>
       <c r="DP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ9" t="n">
-        <v>-0.02781599415017285</v>
+        <v>0.04749886323820533</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0002163568278280296</v>
+        <v>-0.0008081653926758865</v>
       </c>
       <c r="DS9" t="n">
         <v>0</v>
@@ -5357,82 +5357,82 @@
         <v>-0</v>
       </c>
       <c r="DV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001170596689471825</v>
+        <v>0.02509071785534893</v>
       </c>
       <c r="DY9" t="n">
         <v>0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>-0.06159511086322306</v>
+        <v>0.02179360691518919</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01277477942149955</v>
+        <v>-0.033173163674864</v>
       </c>
       <c r="EB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.003995118857192442</v>
+        <v>-0.00363955290272379</v>
       </c>
       <c r="EH9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.07354526679419983</v>
+        <v>0.05262038225784769</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.04663789603508074</v>
+        <v>0.04161354373944651</v>
       </c>
       <c r="EK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL9" t="n">
         <v>-0</v>
       </c>
       <c r="EM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN9" t="n">
         <v>-0</v>
       </c>
       <c r="EO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.08289450129499981</v>
+        <v>-0.04230908239354365</v>
       </c>
       <c r="EQ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER9" t="n">
-        <v>-0.06452548441508707</v>
+        <v>-0.03844063761699726</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01177948182984246</v>
+        <v>0.003891089290326568</v>
       </c>
       <c r="ET9" t="n">
         <v>-0</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,49 +5444,49 @@
         <v>-0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.05575798335214243</v>
+        <v>-0.06240168734101381</v>
       </c>
       <c r="EZ9" t="n">
         <v>-0</v>
       </c>
       <c r="FA9" t="n">
-        <v>0.03062273268441391</v>
+        <v>0.06709607193869617</v>
       </c>
       <c r="FB9" t="n">
-        <v>0.007642498349471457</v>
+        <v>0.01283072744507583</v>
       </c>
       <c r="FC9" t="n">
         <v>-0</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF9" t="n">
         <v>-0</v>
       </c>
       <c r="FG9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH9" t="n">
-        <v>0.03111639733926996</v>
+        <v>-0.01214779492382731</v>
       </c>
       <c r="FI9" t="n">
         <v>-0</v>
       </c>
       <c r="FJ9" t="n">
-        <v>0.06760339432032428</v>
+        <v>-0.01224984785728085</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.03588874853998237</v>
+        <v>-0.0297943022347699</v>
       </c>
       <c r="FL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN9" t="n">
         <v>-0</v>
@@ -5495,46 +5495,46 @@
         <v>-0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.04400671252846972</v>
+        <v>0.004017367030521993</v>
       </c>
       <c r="FR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS9" t="n">
-        <v>-0.004982085057918361</v>
+        <v>0.03978509774912406</v>
       </c>
       <c r="FT9" t="n">
-        <v>0.09649272571852938</v>
+        <v>-0.0861763676206703</v>
       </c>
       <c r="FU9" t="n">
         <v>-0</v>
       </c>
       <c r="FV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
         <v>0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>-0.02596322865274908</v>
+        <v>-0.03277893262568786</v>
       </c>
       <c r="GA9" t="n">
         <v>-0</v>
       </c>
       <c r="GB9" t="n">
-        <v>-0.0285355953398962</v>
+        <v>-0.006834662592566978</v>
       </c>
       <c r="GC9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,25 +5554,25 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5407111251145273</v>
+        <v>0.188621404605109</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2016399133246066</v>
+        <v>-0.2041917282494197</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1350959168775636</v>
+        <v>-0.09420281453599666</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G10" t="n">
         <v>-0</v>
       </c>
       <c r="H10" t="n">
-        <v>0.003852032474455218</v>
+        <v>0.003431338762926186</v>
       </c>
       <c r="I10" t="n">
         <v>-0</v>
@@ -5581,25 +5581,25 @@
         <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2773289776739223</v>
+        <v>0.1179081182855745</v>
       </c>
       <c r="L10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.2499043703245696</v>
+        <v>-0.3697348812887656</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.2464411654557337</v>
+        <v>-0.1544686993145824</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.001554485570413537</v>
+        <v>0.001145511813682986</v>
       </c>
       <c r="R10" t="n">
         <v>-0</v>
@@ -5608,16 +5608,16 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1124211081738318</v>
+        <v>0.06924999375931959</v>
       </c>
       <c r="U10" t="n">
         <v>-0</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.04740922299625878</v>
+        <v>-0.06318260811293414</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.06059242954990575</v>
+        <v>-0.09879902797197911</v>
       </c>
       <c r="X10" t="n">
         <v>-0</v>
@@ -5626,142 +5626,142 @@
         <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.009589959168939167</v>
+        <v>0.02053583155871988</v>
       </c>
       <c r="AA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.07778910881359896</v>
+        <v>-0.04873927592292399</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.08998509583996964</v>
+        <v>-0.05484981582702955</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.07981084100016018</v>
+        <v>-0.03504398983118671</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.630263676318253e-11</v>
+        <v>1.227832166930565e-10</v>
       </c>
       <c r="AJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>-0.004025892854037009</v>
+        <v>0.1811845223964433</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
       </c>
       <c r="AN10" t="n">
-        <v>-0.08992958786047296</v>
+        <v>-0.0176690079909182</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.2034797207508635</v>
+        <v>0.04999562342245465</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
       </c>
       <c r="AQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.05155070527039243</v>
+        <v>-0.01509389318117213</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT10" t="n">
         <v>-0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.9163430920870876</v>
+        <v>0.3178275458362777</v>
       </c>
       <c r="AV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.05972301842178926</v>
+        <v>-0.03900962143310221</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.292336155957983</v>
+        <v>-0.360893061821076</v>
       </c>
       <c r="AY10" t="n">
         <v>-0</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.1009363817088652</v>
+        <v>-0.09467183975094541</v>
       </c>
       <c r="BB10" t="n">
         <v>-0</v>
       </c>
       <c r="BC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.006289136114339917</v>
+        <v>-0.06262670076959517</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
       </c>
       <c r="BF10" t="n">
-        <v>-0.09290761586745611</v>
+        <v>-0.163673849013343</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.2539450282035305</v>
+        <v>-0.01843193132666457</v>
       </c>
       <c r="BH10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BI10" t="n">
         <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.01222240947604272</v>
+        <v>-0.03296183921354995</v>
       </c>
       <c r="BK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL10" t="n">
         <v>-0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.390266612368925</v>
+        <v>0.0830878025108059</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.1793660712206083</v>
+        <v>0.08600103661120603</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.2957341931719327</v>
+        <v>0.04680405702998705</v>
       </c>
       <c r="BQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
-        <v>0.08343488714931932</v>
+        <v>0.07305423687256617</v>
       </c>
       <c r="BT10" t="n">
         <v>-0</v>
@@ -5770,205 +5770,205 @@
         <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.4441993544171567</v>
+        <v>0.2127484172081274</v>
       </c>
       <c r="BW10" t="n">
         <v>-0</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.01742247662862836</v>
+        <v>-0.03859346865304113</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.03281467687235599</v>
+        <v>-0.2748220517893951</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
       </c>
       <c r="CB10" t="n">
-        <v>-0.0233986793582012</v>
+        <v>-0.131090925670871</v>
       </c>
       <c r="CC10" t="n">
         <v>-0</v>
       </c>
       <c r="CD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.130297370895971</v>
+        <v>-0.05914128067118286</v>
       </c>
       <c r="CF10" t="n">
         <v>-0</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.001479845025411586</v>
+        <v>0.1146668065490267</v>
       </c>
       <c r="CH10" t="n">
-        <v>-0.02046022589911825</v>
+        <v>0.03729213299089341</v>
       </c>
       <c r="CI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ10" t="n">
         <v>-0</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.01572128557282828</v>
+        <v>-0.03025138958167831</v>
       </c>
       <c r="CL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM10" t="n">
         <v>0</v>
       </c>
       <c r="CN10" t="n">
-        <v>-0.2061889370517557</v>
+        <v>-0.03127721295148398</v>
       </c>
       <c r="CO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>-0.245654472780435</v>
+        <v>0.2433197410276782</v>
       </c>
       <c r="CQ10" t="n">
-        <v>-0.09170255564705031</v>
+        <v>0.277337083057869</v>
       </c>
       <c r="CR10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.1377335021579791</v>
+        <v>0.02119180751216638</v>
       </c>
       <c r="CU10" t="n">
         <v>0</v>
       </c>
       <c r="CV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.07915332093516005</v>
+        <v>-0.04916773693621702</v>
       </c>
       <c r="CX10" t="n">
         <v>0</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.05764602845909789</v>
+        <v>0.1450521189923607</v>
       </c>
       <c r="CZ10" t="n">
-        <v>-0.01285575189627416</v>
+        <v>0.0630767497260734</v>
       </c>
       <c r="DA10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB10" t="n">
         <v>0</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.01213644830901321</v>
+        <v>-0.02591742100518285</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.05676158040014594</v>
+        <v>-0.01564373991799128</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.03201839626103923</v>
+        <v>0.05773648043298635</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.01907826590593834</v>
+        <v>-0.01241363588445519</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK10" t="n">
         <v>-0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0.001326446167532763</v>
+        <v>-0.03954080387010134</v>
       </c>
       <c r="DM10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.1220463514517836</v>
+        <v>-0.03519856555204192</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0.03572346473703963</v>
+        <v>0.06670206865422122</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.06786035729228607</v>
+        <v>-0.143146098355007</v>
       </c>
       <c r="DS10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0.05214582253672739</v>
+        <v>0.1076155374522183</v>
       </c>
       <c r="DV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.09366163018058023</v>
+        <v>0.09206610038141183</v>
       </c>
       <c r="DY10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ10" t="n">
-        <v>-0.05467398866148412</v>
+        <v>0.09894191769985994</v>
       </c>
       <c r="EA10" t="n">
-        <v>-0.1183066487304788</v>
+        <v>-0.08220299561967383</v>
       </c>
       <c r="EB10" t="n">
         <v>0</v>
       </c>
       <c r="EC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED10" t="n">
-        <v>-0.0218425263726557</v>
+        <v>0.1601270482641556</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.05074081903308744</v>
+        <v>-0.01652518485339773</v>
       </c>
       <c r="EH10" t="n">
         <v>-0</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.07082482162234234</v>
+        <v>0.0961118293367193</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.041900222996049</v>
+        <v>0.009226901168210296</v>
       </c>
       <c r="EK10" t="n">
         <v>0</v>
@@ -5977,52 +5977,52 @@
         <v>-0</v>
       </c>
       <c r="EM10" t="n">
-        <v>0.05821442132301583</v>
+        <v>-0.02588153774358583</v>
       </c>
       <c r="EN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO10" t="n">
         <v>0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.1514852490998026</v>
+        <v>-0.004391826143365958</v>
       </c>
       <c r="EQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.08964805177864447</v>
+        <v>0.11027399400449</v>
       </c>
       <c r="ES10" t="n">
-        <v>-0.1011519746163665</v>
+        <v>0.01328285518078614</v>
       </c>
       <c r="ET10" t="n">
         <v>-0</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
-        <v>-0.03100679235386417</v>
+        <v>-0.008543591345452729</v>
       </c>
       <c r="EW10" t="n">
         <v>-0</v>
       </c>
       <c r="EX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.09091246485789266</v>
+        <v>-0.0819945317174801</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.02648257686023893</v>
+        <v>0.1663376578935969</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.04341268816959238</v>
+        <v>0.04252876653070782</v>
       </c>
       <c r="FC10" t="n">
         <v>-0</v>
@@ -6031,7 +6031,7 @@
         <v>-0</v>
       </c>
       <c r="FE10" t="n">
-        <v>0.005310696963633347</v>
+        <v>-0.01125859651102088</v>
       </c>
       <c r="FF10" t="n">
         <v>-0</v>
@@ -6040,16 +6040,16 @@
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.08135764934729958</v>
+        <v>0.006665657835292597</v>
       </c>
       <c r="FI10" t="n">
         <v>0</v>
       </c>
       <c r="FJ10" t="n">
-        <v>-0.06443371753654847</v>
+        <v>-0.05340754334572025</v>
       </c>
       <c r="FK10" t="n">
-        <v>-0.03892800051942179</v>
+        <v>0.116065133804438</v>
       </c>
       <c r="FL10" t="n">
         <v>0</v>
@@ -6058,25 +6058,25 @@
         <v>-0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0.009201381573407604</v>
+        <v>0.004309471861362024</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
       </c>
       <c r="FP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>-0.2594821626120333</v>
+        <v>0.06917783291364002</v>
       </c>
       <c r="FR10" t="n">
         <v>0</v>
       </c>
       <c r="FS10" t="n">
-        <v>-0.2193682741471389</v>
+        <v>0.1130528003173031</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.1624908043852578</v>
+        <v>-0.2446719644079264</v>
       </c>
       <c r="FU10" t="n">
         <v>-0</v>
@@ -6085,34 +6085,34 @@
         <v>0</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.03992196136991334</v>
+        <v>-0.06415638217818195</v>
       </c>
       <c r="FX10" t="n">
         <v>0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>-0.1518724883824849</v>
+        <v>-0.05388919593673746</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
-        <v>-0.08995590047039734</v>
+        <v>0.05447907155848965</v>
       </c>
       <c r="GC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.0914328864948992</v>
+        <v>0.001365184540242252</v>
       </c>
       <c r="GG10" t="n">
         <v>-0</v>
@@ -6123,25 +6123,25 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.1264982660824506</v>
+        <v>0.2948874702287342</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1010416475286456</v>
+        <v>-0.02425741075439546</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.06736178046966328</v>
+        <v>-0.1662859861257134</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -6150,7 +6150,7 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.06755406581919619</v>
+        <v>0.3529937908330402</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -6159,13 +6159,13 @@
         <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.09686343083522156</v>
+        <v>-0.08820823547932534</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.06783245527839372</v>
+        <v>-0.1283914506806732</v>
       </c>
       <c r="P11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,7 +6177,7 @@
         <v>-0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0246044396895783</v>
+        <v>0.06592360626212566</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -6186,10 +6186,10 @@
         <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.01280331966404087</v>
+        <v>-0.07304815721946893</v>
       </c>
       <c r="X11" t="n">
-        <v>0.02531186438114293</v>
+        <v>0.01610492290740674</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
@@ -6198,25 +6198,25 @@
         <v>-0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB11" t="n">
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.02624000718326293</v>
+        <v>-0.01718318899230262</v>
       </c>
       <c r="AD11" t="n">
         <v>-0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.02053932422090534</v>
+        <v>-0.159783948646993</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.01831923465805918</v>
+        <v>0.0258013878640735</v>
       </c>
       <c r="AH11" t="n">
         <v>-0</v>
@@ -6231,7 +6231,7 @@
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.03019000208390693</v>
+        <v>0.07737660748912639</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
@@ -6240,106 +6240,106 @@
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.02167828261374442</v>
+        <v>-0.0730285766389704</v>
       </c>
       <c r="AP11" t="n">
-        <v>-0.005103666240848554</v>
+        <v>-0.03818767249138202</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.1644029439479651</v>
+        <v>0.5275933023758904</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW11" t="n">
         <v>0</v>
       </c>
       <c r="AX11" t="n">
-        <v>-0.02817208851656468</v>
+        <v>-0.2077733752482235</v>
       </c>
       <c r="AY11" t="n">
-        <v>-0.01552788845842532</v>
+        <v>-0.05016657864281078</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC11" t="n">
         <v>0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.02749511806433985</v>
+        <v>-0.04501002307227175</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.06488224516061489</v>
+        <v>-0.0188968514122638</v>
       </c>
       <c r="BH11" t="n">
-        <v>-0.0398422682148595</v>
+        <v>-0.07365784946961169</v>
       </c>
       <c r="BI11" t="n">
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
       </c>
       <c r="BL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.08018258151658449</v>
+        <v>0.1514358241533841</v>
       </c>
       <c r="BN11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO11" t="n">
         <v>-0</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.05336656014177592</v>
+        <v>0.1556464901239507</v>
       </c>
       <c r="BQ11" t="n">
-        <v>0.02217172442641558</v>
+        <v>0.09761107549834516</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>-0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.06642295344740001</v>
+        <v>0.3385088744498972</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
@@ -6348,43 +6348,43 @@
         <v>0</v>
       </c>
       <c r="BY11" t="n">
-        <v>-0.02294950271410317</v>
+        <v>-0.08504819471434938</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.005956819455632601</v>
+        <v>-0.04419666824292227</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.02668282347523912</v>
+        <v>-0.1148772877710088</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.01484024229332514</v>
+        <v>0.003776502211223746</v>
       </c>
       <c r="CI11" t="n">
-        <v>0.02097025433599488</v>
+        <v>0.07075926507626981</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL11" t="n">
         <v>-0</v>
@@ -6393,22 +6393,22 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.0310221355225829</v>
+        <v>-0.2330472082267131</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
         <v>-0</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.02736188727869271</v>
+        <v>0.05743799549345353</v>
       </c>
       <c r="CR11" t="n">
-        <v>-0.002423552755429784</v>
+        <v>0.01341525150398345</v>
       </c>
       <c r="CS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT11" t="n">
         <v>-0</v>
@@ -6417,28 +6417,28 @@
         <v>0</v>
       </c>
       <c r="CV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.01302092842841177</v>
+        <v>-0.09896519728607582</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
         <v>0</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.01350314037955262</v>
+        <v>-0.01718535499254884</v>
       </c>
       <c r="DA11" t="n">
-        <v>0.02421051553341514</v>
+        <v>0.07286126697603341</v>
       </c>
       <c r="DB11" t="n">
         <v>0</v>
       </c>
       <c r="DC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD11" t="n">
         <v>0</v>
@@ -6447,7 +6447,7 @@
         <v>-0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.02274368922650078</v>
+        <v>-0.09520610937383829</v>
       </c>
       <c r="DG11" t="n">
         <v>-0</v>
@@ -6456,37 +6456,37 @@
         <v>-0</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.01432290195943902</v>
+        <v>-0.1324066633837949</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.006114630458516354</v>
+        <v>-0.01624002240867987</v>
       </c>
       <c r="DK11" t="n">
         <v>0</v>
       </c>
       <c r="DL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN11" t="n">
         <v>-0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.02508077785186991</v>
+        <v>-0.06022351560850037</v>
       </c>
       <c r="DP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ11" t="n">
         <v>0</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0195510493817696</v>
+        <v>-0.03054885154624309</v>
       </c>
       <c r="DS11" t="n">
-        <v>-0.03512511100117643</v>
+        <v>-0.01421123569455499</v>
       </c>
       <c r="DT11" t="n">
         <v>-0</v>
@@ -6501,7 +6501,7 @@
         <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0006908908836452184</v>
+        <v>0.07317556696613665</v>
       </c>
       <c r="DY11" t="n">
         <v>0</v>
@@ -6510,124 +6510,124 @@
         <v>-0</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.03699875369452738</v>
+        <v>-0.008946800438323559</v>
       </c>
       <c r="EB11" t="n">
-        <v>-0.01670401354666498</v>
+        <v>0.03950731427375075</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
         <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.005659020484685309</v>
+        <v>0.01270399047469997</v>
       </c>
       <c r="EH11" t="n">
         <v>-0</v>
       </c>
       <c r="EI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.005979249545618404</v>
+        <v>-0.06445808790326077</v>
       </c>
       <c r="EK11" t="n">
-        <v>0.007850707283415538</v>
+        <v>0.06409176166202826</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
         <v>-0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.01505174058034706</v>
+        <v>0.008524195885199967</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
         <v>0</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.002408284378346959</v>
+        <v>-0.1451520156590778</v>
       </c>
       <c r="ET11" t="n">
-        <v>0.02596231707677813</v>
+        <v>0.0535977060079697</v>
       </c>
       <c r="EU11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW11" t="n">
         <v>0</v>
       </c>
       <c r="EX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.008566828047975053</v>
+        <v>-0.1290964218206297</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.01299818816672416</v>
+        <v>-0.03160170986624868</v>
       </c>
       <c r="FC11" t="n">
-        <v>0.02856701427894971</v>
+        <v>0.0531834183157868</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF11" t="n">
         <v>-0</v>
       </c>
       <c r="FG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.02584560463323945</v>
+        <v>-0.1289129015141905</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
         <v>-0</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03822142963612288</v>
+        <v>0.145647589226127</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.02033609638763326</v>
+        <v>0.04026081642038985</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
         <v>0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.009173335735800587</v>
+        <v>0.06561234518258008</v>
       </c>
       <c r="FR11" t="n">
         <v>0</v>
@@ -6645,25 +6645,25 @@
         <v>-0</v>
       </c>
       <c r="FT11" t="n">
-        <v>-0.01972457043563238</v>
+        <v>-0.1170247012623718</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.02007050360524771</v>
+        <v>-0.01187793958750624</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.04368531969031271</v>
+        <v>-0.05618547330377519</v>
       </c>
       <c r="GA11" t="n">
         <v>0</v>
@@ -6675,7 +6675,7 @@
         <v>-0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0.008854992949508407</v>
+        <v>0.08941757315320591</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
@@ -6692,16 +6692,16 @@
         <v>0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.356105925027107</v>
+        <v>0.3349373813139462</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.3273475644609015</v>
+        <v>-0.20779194399319</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.03510941775715357</v>
+        <v>-0.01943579858401338</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -6719,19 +6719,19 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2273813800921222</v>
+        <v>0.3187714863792417</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3164224570630384</v>
+        <v>-0.2709578667838117</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.08198153896943326</v>
+        <v>-0.05802400138584966</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P12" t="n">
         <v>-0</v>
@@ -6743,22 +6743,22 @@
         <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.07988411165973269</v>
+        <v>0.06021396551389446</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.01804479997848274</v>
+        <v>-0.02067807860526092</v>
       </c>
       <c r="W12" t="n">
-        <v>0.05817906893277577</v>
+        <v>-0.04690615085934316</v>
       </c>
       <c r="X12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
@@ -6770,82 +6770,82 @@
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.1080847864560173</v>
+        <v>-0.06362218811820261</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0.03707943970091036</v>
+        <v>-0.1076123488839624</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.00370144053486786</v>
+        <v>-0.0721947930753904</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.04604551178437569</v>
+        <v>0.1021762746116855</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0.05200083005845777</v>
+        <v>-0.08489892013825029</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.1095944426246499</v>
+        <v>0.05074691449960934</v>
       </c>
       <c r="AP12" t="n">
         <v>0</v>
       </c>
       <c r="AQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.4763181651311523</v>
+        <v>0.278257218766705</v>
       </c>
       <c r="AV12" t="n">
         <v>-0</v>
       </c>
       <c r="AW12" t="n">
-        <v>-0.06335506828253538</v>
+        <v>-0.1227163280145054</v>
       </c>
       <c r="AX12" t="n">
-        <v>0.1412198247482449</v>
+        <v>-0.1771065129421494</v>
       </c>
       <c r="AY12" t="n">
         <v>-0</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
         <v>-0</v>
@@ -6854,16 +6854,16 @@
         <v>0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.0004229954872618721</v>
+        <v>0.008272871049107443</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
       </c>
       <c r="BF12" t="n">
-        <v>-0.1186142366160628</v>
+        <v>-0.02104211531901017</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.132393745598824</v>
+        <v>0.001722052786951889</v>
       </c>
       <c r="BH12" t="n">
         <v>0</v>
@@ -6872,7 +6872,7 @@
         <v>-0</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK12" t="n">
         <v>0</v>
@@ -6881,22 +6881,22 @@
         <v>-0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.1246896416856042</v>
+        <v>-0.006994452701001755</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.05607087927436529</v>
+        <v>0.0446188413247626</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.1450592201036958</v>
+        <v>0.07319341279846961</v>
       </c>
       <c r="BQ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
         <v>-0</v>
@@ -6908,25 +6908,25 @@
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.2056107721507822</v>
+        <v>0.2325403309344716</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>-0.0276442048634645</v>
+        <v>-0.05525933354815486</v>
       </c>
       <c r="BY12" t="n">
-        <v>0.0926420225689817</v>
+        <v>-0.03564222222022844</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>0</v>
@@ -6935,46 +6935,46 @@
         <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.07575994655083948</v>
+        <v>-0.1040942724699113</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
-        <v>0.02927118341516405</v>
+        <v>0.1195960785568957</v>
       </c>
       <c r="CH12" t="n">
-        <v>-0.02539130996499756</v>
+        <v>0.002790818345307438</v>
       </c>
       <c r="CI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>-0.0448773233779386</v>
+        <v>-0.08360712539584413</v>
       </c>
       <c r="CO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP12" t="n">
-        <v>-0.197826330564627</v>
+        <v>0.1743704016603309</v>
       </c>
       <c r="CQ12" t="n">
-        <v>-0.08757642132000598</v>
+        <v>0.03752421913505668</v>
       </c>
       <c r="CR12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS12" t="n">
         <v>-0</v>
@@ -6983,55 +6983,55 @@
         <v>-0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.04451413814147292</v>
+        <v>-0.102472794864821</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
-        <v>0.05163792271698823</v>
+        <v>0.1227880354262004</v>
       </c>
       <c r="CZ12" t="n">
-        <v>-0.01329956497643998</v>
+        <v>0.0109995784416012</v>
       </c>
       <c r="DA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
       </c>
       <c r="DC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD12" t="n">
         <v>0</v>
       </c>
       <c r="DE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DF12" t="n">
-        <v>-0.01112579202634385</v>
+        <v>-0.1078506140745537</v>
       </c>
       <c r="DG12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH12" t="n">
-        <v>0.02287306999489502</v>
+        <v>0.01834499731075623</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.03701593632784823</v>
+        <v>-0.05703647113038848</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL12" t="n">
         <v>0</v>
@@ -7043,22 +7043,22 @@
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.03619825339398167</v>
+        <v>-0.07360147925057467</v>
       </c>
       <c r="DP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ12" t="n">
-        <v>0.04055421436266991</v>
+        <v>0.04352655079466326</v>
       </c>
       <c r="DR12" t="n">
-        <v>-0.03603307586464365</v>
+        <v>-0.003679441451304843</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU12" t="n">
         <v>-0</v>
@@ -7070,76 +7070,76 @@
         <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>0.02985293618991007</v>
+        <v>-0.005880937387766671</v>
       </c>
       <c r="DY12" t="n">
         <v>0</v>
       </c>
       <c r="DZ12" t="n">
-        <v>0.05610893983687579</v>
+        <v>-0.05657094774104399</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.01112703613313716</v>
+        <v>0.05875680799032469</v>
       </c>
       <c r="EB12" t="n">
         <v>-0</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.01783664752591511</v>
+        <v>-0.05817921007092546</v>
       </c>
       <c r="EH12" t="n">
         <v>-0</v>
       </c>
       <c r="EI12" t="n">
-        <v>0.08495298685785083</v>
+        <v>0.09338834314583393</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.05435229773281496</v>
+        <v>0.03889276078535478</v>
       </c>
       <c r="EK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN12" t="n">
         <v>-0</v>
       </c>
       <c r="EO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.07967318855358811</v>
+        <v>-0.03819466494002983</v>
       </c>
       <c r="EQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER12" t="n">
-        <v>0.01817578624549318</v>
+        <v>0.06600166473074109</v>
       </c>
       <c r="ES12" t="n">
-        <v>0.06222577699490948</v>
+        <v>-0.04076971088967053</v>
       </c>
       <c r="ET12" t="n">
         <v>-0</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,43 +7151,43 @@
         <v>-0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.0551760051377822</v>
+        <v>-0.1182261062042901</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
       </c>
       <c r="FA12" t="n">
-        <v>0.04206832536128274</v>
+        <v>0.1389204867051448</v>
       </c>
       <c r="FB12" t="n">
-        <v>-0.0005613731767063897</v>
+        <v>-0.008152718023957716</v>
       </c>
       <c r="FC12" t="n">
         <v>-0</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>-0</v>
       </c>
       <c r="FH12" t="n">
-        <v>0.03168485946606039</v>
+        <v>-0.1152662320505733</v>
       </c>
       <c r="FI12" t="n">
         <v>-0</v>
       </c>
       <c r="FJ12" t="n">
-        <v>0.05355426045263198</v>
+        <v>0.09028559460101346</v>
       </c>
       <c r="FK12" t="n">
-        <v>-0.03027493138111739</v>
+        <v>0.04007563812087079</v>
       </c>
       <c r="FL12" t="n">
         <v>0</v>
@@ -7196,64 +7196,64 @@
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP12" t="n">
         <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.03326493599153122</v>
+        <v>0.007228300385904077</v>
       </c>
       <c r="FR12" t="n">
         <v>0</v>
       </c>
       <c r="FS12" t="n">
-        <v>-0.06418374001985755</v>
+        <v>0.117958831051226</v>
       </c>
       <c r="FT12" t="n">
-        <v>0.04156068006899397</v>
+        <v>-0.03726230582246329</v>
       </c>
       <c r="FU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW12" t="n">
         <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>0.03072773072611829</v>
+        <v>-0.08049674885934621</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
-        <v>-0.08360481121215224</v>
+        <v>0.06040379379664235</v>
       </c>
       <c r="GC12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
       </c>
       <c r="GF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,19 +7261,19 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.4562722459161241</v>
+        <v>0.4548459992461376</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
         <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1161644569419592</v>
+        <v>0.03975578625320947</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.3380762144340904</v>
+        <v>-0.3453312094646123</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -7288,25 +7288,25 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3181731283336343</v>
+        <v>0.6097906663533501</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M13" t="n">
         <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0929885288576002</v>
+        <v>-0.05177193625183561</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3166656802397269</v>
+        <v>-0.3370545626272469</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -7315,25 +7315,25 @@
         <v>-0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.06904277453375565</v>
+        <v>0.1720374956507761</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.01692962264278432</v>
+        <v>-0.1589792398289766</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01340659289609996</v>
+        <v>0.002368903377557166</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -7342,19 +7342,19 @@
         <v>-0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05865255926861281</v>
+        <v>-0.03477837227442231</v>
       </c>
       <c r="AD13" t="n">
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.0444993440285001</v>
+        <v>-0.3771723006800006</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.0128475004527829</v>
+        <v>-0.181005988627594</v>
       </c>
       <c r="AH13" t="n">
         <v>-0</v>
@@ -7363,28 +7363,28 @@
         <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.08258948347264849</v>
+        <v>0.09853447578761491</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.00149602596424211</v>
+        <v>-0.008109623410809244</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.06719702132353282</v>
+        <v>-0.2042905382066797</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR13" t="n">
         <v>-0</v>
@@ -7393,10 +7393,10 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.4186827764955669</v>
+        <v>0.9360374111527487</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
@@ -7405,43 +7405,43 @@
         <v>0</v>
       </c>
       <c r="AX13" t="n">
-        <v>-0.04596529706862233</v>
+        <v>-0.2140773623736242</v>
       </c>
       <c r="AY13" t="n">
-        <v>-0.1760270418060803</v>
+        <v>-0.1709140324118987</v>
       </c>
       <c r="AZ13" t="n">
         <v>0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.1009726169460692</v>
+        <v>-0.1548257033423101</v>
       </c>
       <c r="BE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BF13" t="n">
         <v>0</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1007323412607164</v>
+        <v>-0.1911798749866495</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.092844102698831</v>
+        <v>-0.1746819412469815</v>
       </c>
       <c r="BI13" t="n">
         <v>0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,52 +7450,52 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.1484047786471922</v>
+        <v>0.1680999546885465</v>
       </c>
       <c r="BN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO13" t="n">
         <v>-0</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.08049809434016349</v>
+        <v>0.1737981132482635</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03238267468314128</v>
+        <v>-0.01702148442859939</v>
       </c>
       <c r="BR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS13" t="n">
         <v>0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.2106581889126529</v>
+        <v>0.4789320734609512</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
         <v>0</v>
       </c>
       <c r="BY13" t="n">
-        <v>-0.05685201156288592</v>
+        <v>-0.09575770769789885</v>
       </c>
       <c r="BZ13" t="n">
-        <v>-0.1116816034443778</v>
+        <v>-0.2232332342565743</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>0</v>
@@ -7504,49 +7504,49 @@
         <v>-0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.09674752841934435</v>
+        <v>-0.1900784150537115</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
         <v>-0</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.01134797682010751</v>
+        <v>0.05405442945178832</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.08012059290730283</v>
+        <v>0.1497969486889981</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
       </c>
       <c r="CL13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM13" t="n">
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.07420046722858696</v>
+        <v>-0.4021050849784559</v>
       </c>
       <c r="CO13" t="n">
         <v>0</v>
       </c>
       <c r="CP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.04077179232027319</v>
+        <v>0.421193402147501</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.02971217695521739</v>
+        <v>0.3454184703950743</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
         <v>-0</v>
@@ -7558,19 +7558,19 @@
         <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.07356795108112858</v>
+        <v>-0.1791463053894608</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
         <v>0</v>
       </c>
       <c r="CZ13" t="n">
-        <v>-0.005525380232076612</v>
+        <v>0.009957822893613574</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.08645943743018089</v>
+        <v>0.1297204317757895</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7582,55 +7582,55 @@
         <v>0</v>
       </c>
       <c r="DE13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.06652959088449979</v>
+        <v>-0.01879688781600164</v>
       </c>
       <c r="DG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.05529090818379761</v>
+        <v>-0.1815723646066356</v>
       </c>
       <c r="DJ13" t="n">
-        <v>-0.008999608973962254</v>
+        <v>0.02291206513115465</v>
       </c>
       <c r="DK13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL13" t="n">
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.05351740294952523</v>
+        <v>0.002019950471933863</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR13" t="n">
-        <v>0.02267360403353078</v>
+        <v>-0.0235598792935672</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.006830711728326886</v>
+        <v>0.08746494150722811</v>
       </c>
       <c r="DT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,25 +7639,25 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>0.002210282527747582</v>
+        <v>0.1705983879505248</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
         <v>-0</v>
       </c>
       <c r="EA13" t="n">
-        <v>-0.002720787191998843</v>
+        <v>-0.06104859259515889</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.009466639627989673</v>
+        <v>0.03373162864371534</v>
       </c>
       <c r="EC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
         <v>-0</v>
@@ -7666,19 +7666,19 @@
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.03307553149186553</v>
+        <v>-0.0556021572906517</v>
       </c>
       <c r="EH13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.0199587095951503</v>
+        <v>-0.04104859203090219</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.08136357239273918</v>
+        <v>-0.01550955407667653</v>
       </c>
       <c r="EL13" t="n">
         <v>-0</v>
@@ -7687,13 +7687,13 @@
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.01737974599884997</v>
+        <v>-0.03522995917223581</v>
       </c>
       <c r="EQ13" t="n">
         <v>0</v>
@@ -7702,10 +7702,10 @@
         <v>-0</v>
       </c>
       <c r="ES13" t="n">
-        <v>-0.0314498837592302</v>
+        <v>-0.08351713168789197</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.07718296283963495</v>
+        <v>0.1463723189019243</v>
       </c>
       <c r="EU13" t="n">
         <v>-0</v>
@@ -7717,10 +7717,10 @@
         <v>-0</v>
       </c>
       <c r="EX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.06422638237392678</v>
+        <v>-0.2152508884882436</v>
       </c>
       <c r="EZ13" t="n">
         <v>0</v>
@@ -7729,64 +7729,64 @@
         <v>-0</v>
       </c>
       <c r="FB13" t="n">
-        <v>-0.01045294116400082</v>
+        <v>-0.01658317422362405</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.0872925751927735</v>
+        <v>0.1342846940928669</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
       </c>
       <c r="FF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.06998371113217733</v>
+        <v>-0.1642104946956362</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
         <v>-0</v>
       </c>
       <c r="FK13" t="n">
-        <v>-0.01960058257004734</v>
+        <v>0.1051051006159296</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.0659647983907895</v>
+        <v>-0.1383597957278391</v>
       </c>
       <c r="FM13" t="n">
         <v>0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>0.01084695572953623</v>
+        <v>0.04314259741249324</v>
       </c>
       <c r="FR13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS13" t="n">
         <v>-0</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.04836904612322503</v>
+        <v>0.02928490453625475</v>
       </c>
       <c r="FU13" t="n">
-        <v>-0.01100046938879572</v>
+        <v>-0.03421832450862223</v>
       </c>
       <c r="FV13" t="n">
         <v>-0</v>
@@ -7795,25 +7795,25 @@
         <v>0</v>
       </c>
       <c r="FX13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>-0.04179229178010763</v>
+        <v>-0.07120316278884858</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
         <v>-0</v>
       </c>
       <c r="GC13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.04359218957911182</v>
+        <v>0.01562834224324661</v>
       </c>
       <c r="GE13" t="n">
         <v>-0</v>
@@ -7822,7 +7822,7 @@
         <v>-0</v>
       </c>
       <c r="GG13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -7830,16 +7830,16 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.8688484855603391</v>
+        <v>0.2678076170050281</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3501684230490169</v>
+        <v>-0.1893291983788999</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.2589324656966952</v>
+        <v>-0.04898267016433162</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -7851,22 +7851,22 @@
         <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.5201682979624286</v>
+        <v>0.3154017457126403</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.3341675719261765</v>
+        <v>-0.2688736615480669</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.2358866312271939</v>
+        <v>-0.1280230176117731</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -7881,73 +7881,73 @@
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.1975616790300831</v>
+        <v>0.07701409947706049</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.07130552257903461</v>
+        <v>-0.04969534935193339</v>
       </c>
       <c r="W14" t="n">
-        <v>0.03925992351895414</v>
+        <v>-0.09979479058762473</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.07216156297882664</v>
+        <v>-0.01341199359051659</v>
       </c>
       <c r="AD14" t="n">
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0.007171677741329001</v>
+        <v>-0.2262804656666259</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.005816602575164124</v>
+        <v>-0.1270222789165104</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL14" t="n">
-        <v>0.06104590672916133</v>
+        <v>0.1793516236585046</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.09481155950382329</v>
+        <v>-0.1129875706787671</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.1290821174328996</v>
+        <v>0.0961248031778256</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
@@ -7965,25 +7965,25 @@
         <v>-0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.7350957387530772</v>
+        <v>0.4489579226221123</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02098291001476535</v>
+        <v>-0.01639676195399687</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.0619421154805032</v>
+        <v>-0.2591377680108763</v>
       </c>
       <c r="AY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
@@ -7992,49 +7992,49 @@
         <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.04989250965980249</v>
+        <v>-0.08212564273433914</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.2239209297335207</v>
+        <v>-0.09174787269689588</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.2903811981284431</v>
+        <v>0.01189453445836732</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL14" t="n">
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.2123025924947842</v>
+        <v>0.07990959305210905</v>
       </c>
       <c r="BN14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.05421484391733093</v>
+        <v>0.03360264738069069</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.2234989311781893</v>
+        <v>0.1457022942562145</v>
       </c>
       <c r="BQ14" t="n">
         <v>-0</v>
       </c>
       <c r="BR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS14" t="n">
         <v>-0</v>
@@ -8043,49 +8043,49 @@
         <v>-0</v>
       </c>
       <c r="BU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.3763934946056313</v>
+        <v>0.3501428273342684</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.01756266794063113</v>
+        <v>-0.08611430499027596</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.008699489647824458</v>
+        <v>-0.07768893885336754</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.1826759531118414</v>
+        <v>-0.09314869665237131</v>
       </c>
       <c r="CF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>0.03886847771222796</v>
+        <v>0.09721563819945957</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.02161242005270074</v>
+        <v>0.04986578188638308</v>
       </c>
       <c r="CI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ14" t="n">
         <v>-0</v>
@@ -8094,22 +8094,22 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>0.002667718988725054</v>
+        <v>-0.1967438163668379</v>
       </c>
       <c r="CO14" t="n">
         <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.1493305808625107</v>
+        <v>0.2503908775733326</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.1417058966818038</v>
+        <v>0.112655376462194</v>
       </c>
       <c r="CR14" t="n">
         <v>0</v>
@@ -8118,28 +8118,28 @@
         <v>-0</v>
       </c>
       <c r="CT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV14" t="n">
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.1496696466870169</v>
+        <v>-0.06892593181226647</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.07738209858978728</v>
+        <v>0.1235971124714187</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.02388805394506988</v>
+        <v>0.06470147781751129</v>
       </c>
       <c r="DA14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB14" t="n">
         <v>0</v>
@@ -8148,28 +8148,28 @@
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>0.008766758702662098</v>
+        <v>-0.0004504929958523936</v>
       </c>
       <c r="DG14" t="n">
         <v>0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.04826046580231017</v>
+        <v>0.01181321241108574</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.03762387843891844</v>
+        <v>-0.07592362129680327</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
       </c>
       <c r="DK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL14" t="n">
         <v>0</v>
@@ -8181,79 +8181,79 @@
         <v>-0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.09265018390873017</v>
+        <v>-0.1138839082044336</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.02727828627462141</v>
+        <v>-0.08256754937076455</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.07107973101380249</v>
+        <v>0.02164130465847028</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>0.08962040226558138</v>
+        <v>0.09348553214925462</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.009615914314477428</v>
+        <v>0.005184965430018178</v>
       </c>
       <c r="EA14" t="n">
-        <v>-0.1364902192531859</v>
+        <v>-0.1757743007039735</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
         <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.1464972730228761</v>
+        <v>0.03398912711383965</v>
       </c>
       <c r="EH14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.05109612134898893</v>
+        <v>0.04791748767488982</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.09883759579961381</v>
+        <v>0.0888238244053326</v>
       </c>
       <c r="EK14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL14" t="n">
         <v>-0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
         <v>-0</v>
@@ -8262,22 +8262,22 @@
         <v>0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.08136982820389013</v>
+        <v>-0.01963075792937517</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.02910917252408486</v>
+        <v>0.06707540136750589</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.01492779927241372</v>
+        <v>-0.1101413333961246</v>
       </c>
       <c r="ET14" t="n">
         <v>-0</v>
       </c>
       <c r="EU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV14" t="n">
         <v>0</v>
@@ -8286,52 +8286,52 @@
         <v>-0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.1535436197153204</v>
+        <v>-0.093534500961795</v>
       </c>
       <c r="EZ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>0.05287744815702453</v>
+        <v>0.1226270638282899</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.01604421291359439</v>
+        <v>0.03304801729892017</v>
       </c>
       <c r="FC14" t="n">
         <v>-0</v>
       </c>
       <c r="FD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE14" t="n">
         <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.0008893896483974513</v>
+        <v>0.004818888247293289</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.09958200200361476</v>
+        <v>0.06979675487027399</v>
       </c>
       <c r="FK14" t="n">
-        <v>-0.1239542724331504</v>
+        <v>-0.03702465707792763</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
       </c>
       <c r="FM14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN14" t="n">
         <v>-0</v>
@@ -8340,19 +8340,19 @@
         <v>0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.01275719886208435</v>
+        <v>-0.01112477731616031</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>-0.01915141688514226</v>
+        <v>0.04040998295890679</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.04030502380513516</v>
+        <v>-0.06551677715067419</v>
       </c>
       <c r="FU14" t="n">
         <v>-0</v>
@@ -8361,34 +8361,34 @@
         <v>0</v>
       </c>
       <c r="FW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.03130400704323796</v>
+        <v>-0.07543278853059721</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.09152932145243792</v>
+        <v>0.02357673177104844</v>
       </c>
       <c r="GC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
         <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
         <v>-0</v>
@@ -8399,25 +8399,25 @@
         <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.4897946058250079</v>
+        <v>-0.6243413627762439</v>
       </c>
       <c r="C15" t="n">
         <v>-0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2553873640097842</v>
+        <v>0.1155781253413321</v>
       </c>
       <c r="E15" t="n">
-        <v>0.0912822162339839</v>
+        <v>0.1509359839696592</v>
       </c>
       <c r="F15" t="n">
         <v>-0</v>
       </c>
       <c r="G15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>-0</v>
@@ -8426,43 +8426,43 @@
         <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.3811187252002604</v>
+        <v>-0.5483519545174371</v>
       </c>
       <c r="L15" t="n">
         <v>-0</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2950204349220976</v>
+        <v>0.2385484120195077</v>
       </c>
       <c r="N15" t="n">
-        <v>0.0586984475665568</v>
+        <v>0.2267594508550105</v>
       </c>
       <c r="O15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>-0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>-0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1203263504930447</v>
+        <v>-0.1199517371175563</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.03908782149247531</v>
+        <v>0.08067445765304686</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.0105523830241653</v>
+        <v>-0.04376815611444052</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -8477,52 +8477,52 @@
         <v>-0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>-0.1183005863192267</v>
+        <v>-0.02351710181805735</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0.03765755646461141</v>
+        <v>0.1524128879475702</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.01957589983663047</v>
+        <v>0.0475851185730634</v>
       </c>
       <c r="AG15" t="n">
         <v>-0</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AL15" t="n">
-        <v>-0.06115783779822015</v>
+        <v>-0.3308894899799727</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>0.04097527281714509</v>
+        <v>0.07597748155960633</v>
       </c>
       <c r="AO15" t="n">
-        <v>0.02486619580679795</v>
+        <v>-0.2773860947447516</v>
       </c>
       <c r="AP15" t="n">
         <v>-0</v>
       </c>
       <c r="AQ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8534,19 +8534,19 @@
         <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>-0.3110404540181336</v>
+        <v>-0.5536964712149254</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0.04007913045472587</v>
+        <v>0.05169553706288928</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.0469194117464563</v>
+        <v>0.005960468661062088</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
@@ -8561,16 +8561,16 @@
         <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>-0.07204170637869879</v>
+        <v>0.06271940619969249</v>
       </c>
       <c r="BE15" t="n">
         <v>-0</v>
       </c>
       <c r="BF15" t="n">
-        <v>0.1356385995529577</v>
+        <v>0.09273317016064438</v>
       </c>
       <c r="BG15" t="n">
-        <v>0.2779134401742442</v>
+        <v>0.2934874265087007</v>
       </c>
       <c r="BH15" t="n">
         <v>-0</v>
@@ -8588,43 +8588,43 @@
         <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.02240919932704862</v>
+        <v>0.1241646618396373</v>
       </c>
       <c r="BN15" t="n">
         <v>0</v>
       </c>
       <c r="BO15" t="n">
-        <v>-0.05225952134347327</v>
+        <v>0.0440739516859681</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.05204159306952381</v>
+        <v>0.01016080907851458</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BS15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
         <v>0</v>
       </c>
       <c r="BV15" t="n">
-        <v>-0.2307407669799166</v>
+        <v>-0.468668706924127</v>
       </c>
       <c r="BW15" t="n">
         <v>-0</v>
       </c>
       <c r="BX15" t="n">
-        <v>0.07755213151364411</v>
+        <v>0.07680597409133777</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04382258263362638</v>
+        <v>-0.05013854581592223</v>
       </c>
       <c r="BZ15" t="n">
         <v>-0</v>
@@ -8633,7 +8633,7 @@
         <v>0</v>
       </c>
       <c r="CB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CC15" t="n">
         <v>-0</v>
@@ -8642,46 +8642,46 @@
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>0.1073439045681067</v>
+        <v>0.2736972522215803</v>
       </c>
       <c r="CF15" t="n">
         <v>0</v>
       </c>
       <c r="CG15" t="n">
-        <v>-0.04645352120996245</v>
+        <v>-0.04328732459234678</v>
       </c>
       <c r="CH15" t="n">
-        <v>0.05016834753856157</v>
+        <v>0.00317329170976224</v>
       </c>
       <c r="CI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.03070922391830118</v>
+        <v>0.3117011049615379</v>
       </c>
       <c r="CO15" t="n">
         <v>0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0.003626121778869435</v>
+        <v>-0.1314473646167361</v>
       </c>
       <c r="CQ15" t="n">
-        <v>0.03703803667718018</v>
+        <v>-0.2346701092509987</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CS15" t="n">
         <v>0</v>
@@ -8696,76 +8696,76 @@
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>0.1146223331216115</v>
+        <v>0.2685304543771385</v>
       </c>
       <c r="CX15" t="n">
         <v>-0</v>
       </c>
       <c r="CY15" t="n">
-        <v>-0.054460696297739</v>
+        <v>-0.04980301270195323</v>
       </c>
       <c r="CZ15" t="n">
-        <v>0.03120195477045006</v>
+        <v>-0.007349940687394644</v>
       </c>
       <c r="DA15" t="n">
         <v>-0</v>
       </c>
       <c r="DB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>0.09950553703509149</v>
+        <v>0.06125190503630154</v>
       </c>
       <c r="DG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0.03562441273080511</v>
+        <v>0.009291437125624455</v>
       </c>
       <c r="DI15" t="n">
-        <v>-0.0006922103588113417</v>
+        <v>-0.005598171639212057</v>
       </c>
       <c r="DJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL15" t="n">
         <v>-0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>0</v>
       </c>
       <c r="DO15" t="n">
-        <v>0.1049385743192215</v>
+        <v>0.1463451083054929</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
       </c>
       <c r="DQ15" t="n">
-        <v>-0.07813722559973516</v>
+        <v>0.0252930695922278</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.1160603917489286</v>
+        <v>-0.005827704700185695</v>
       </c>
       <c r="DS15" t="n">
         <v>-0</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
@@ -8774,22 +8774,22 @@
         <v>-0</v>
       </c>
       <c r="DW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.0576246646633161</v>
+        <v>-0.03054990315244763</v>
       </c>
       <c r="DY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0.1224830522733489</v>
+        <v>0.02392758707608936</v>
       </c>
       <c r="EA15" t="n">
-        <v>-0.09141655107188952</v>
+        <v>-0.1043873234062092</v>
       </c>
       <c r="EB15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC15" t="n">
         <v>0</v>
@@ -8804,97 +8804,97 @@
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>0.05424043739083904</v>
+        <v>0.2517858358519689</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
-        <v>-0.03024513164356141</v>
+        <v>-0.03406165434250564</v>
       </c>
       <c r="EJ15" t="n">
-        <v>-0.04013084274520613</v>
+        <v>-0.00952261524942059</v>
       </c>
       <c r="EK15" t="n">
         <v>0</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EN15" t="n">
         <v>-0</v>
       </c>
       <c r="EO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>0.07006353321651008</v>
+        <v>0.17959571234822</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
-        <v>0.04984043352493279</v>
+        <v>-0.004212237535528044</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.07631043686573867</v>
+        <v>-0.0933689448126625</v>
       </c>
       <c r="ET15" t="n">
         <v>0</v>
       </c>
       <c r="EU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX15" t="n">
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>0.1272854826962137</v>
+        <v>0.3122488634807644</v>
       </c>
       <c r="EZ15" t="n">
         <v>0</v>
       </c>
       <c r="FA15" t="n">
-        <v>-0.07084985792562258</v>
+        <v>-0.03663177480272163</v>
       </c>
       <c r="FB15" t="n">
-        <v>0.03204188528670987</v>
+        <v>0.001611838742027666</v>
       </c>
       <c r="FC15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD15" t="n">
         <v>0</v>
       </c>
       <c r="FE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>0.03406443671713183</v>
+        <v>0.1772797020133288</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
-        <v>-0.04911430167798197</v>
+        <v>-0.1018430235702284</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.01469202268249644</v>
+        <v>0.04210312198596278</v>
       </c>
       <c r="FL15" t="n">
         <v>0</v>
@@ -8906,61 +8906,61 @@
         <v>-0</v>
       </c>
       <c r="FO15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP15" t="n">
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>0.01783233709118581</v>
+        <v>0.03338894854483313</v>
       </c>
       <c r="FR15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS15" t="n">
-        <v>0.1498109956087034</v>
+        <v>0.02038769554635566</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.03078288813167587</v>
+        <v>-0.006200091741533267</v>
       </c>
       <c r="FU15" t="n">
         <v>0</v>
       </c>
       <c r="FV15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
         <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.0711471921330625</v>
+        <v>0.1982082442311595</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
-        <v>0.1053542327809655</v>
+        <v>0.08200368469568436</v>
       </c>
       <c r="GC15" t="n">
         <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE15" t="n">
         <v>0</v>
       </c>
       <c r="GF15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="16">
@@ -8971,25 +8971,25 @@
         <v>-0</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.2577959707006281</v>
+        <v>-0.2839338062210509</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3618146944987696</v>
+        <v>0.2224566629548633</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1620365327638392</v>
+        <v>-0.01848256393402597</v>
       </c>
       <c r="F16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -8998,13 +8998,13 @@
         <v>-0</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.15543399211283</v>
+        <v>-0.1835684821001828</v>
       </c>
       <c r="M16" t="n">
-        <v>0.3616650765209314</v>
+        <v>0.2310871906217133</v>
       </c>
       <c r="N16" t="n">
-        <v>0.007069004965059046</v>
+        <v>0.09125735814859498</v>
       </c>
       <c r="O16" t="n">
         <v>-0</v>
@@ -9013,10 +9013,10 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -9025,13 +9025,13 @@
         <v>-0</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.002330486452801787</v>
+        <v>-0.05604267131998004</v>
       </c>
       <c r="V16" t="n">
-        <v>0.07385831159400956</v>
+        <v>0.1485372441138283</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.01159181253437818</v>
+        <v>0.0487608140149025</v>
       </c>
       <c r="X16" t="n">
         <v>-0</v>
@@ -9040,7 +9040,7 @@
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
@@ -9052,13 +9052,13 @@
         <v>-0</v>
       </c>
       <c r="AD16" t="n">
-        <v>-0.04008308330849078</v>
+        <v>-0.01954473061254891</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0.04223230944786743</v>
+        <v>-0.2027376609362497</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.02361417685765593</v>
+        <v>-0.1537097347703596</v>
       </c>
       <c r="AG16" t="n">
         <v>-0</v>
@@ -9070,49 +9070,49 @@
         <v>-0</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.03801006320669476</v>
+        <v>-0.08377799906553449</v>
       </c>
       <c r="AN16" t="n">
-        <v>0.02970872146164135</v>
+        <v>0.1101793510245895</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.04919782110359869</v>
+        <v>0.02942101408954716</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AV16" t="n">
-        <v>-0.140551446294999</v>
+        <v>-0.196689522589939</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.2532404461835556</v>
+        <v>0.3106153257609277</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.2340411727060333</v>
+        <v>-0.09461746784189082</v>
       </c>
       <c r="AY16" t="n">
         <v>0</v>
@@ -9124,22 +9124,22 @@
         <v>-0</v>
       </c>
       <c r="BB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC16" t="n">
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BE16" t="n">
-        <v>-0.05237062105523004</v>
+        <v>-0.01368927111888867</v>
       </c>
       <c r="BF16" t="n">
-        <v>0.06964555788385104</v>
+        <v>-0.2897829868445105</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1061496539400617</v>
+        <v>-0.1016130928548813</v>
       </c>
       <c r="BH16" t="n">
         <v>-0</v>
@@ -9148,163 +9148,163 @@
         <v>0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>-0</v>
       </c>
       <c r="BL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BN16" t="n">
-        <v>0.02940813314501391</v>
+        <v>0.07964268095766158</v>
       </c>
       <c r="BO16" t="n">
-        <v>-0.003434504733069104</v>
+        <v>0.02262234411668058</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.1930407201954022</v>
+        <v>0.1683411012503334</v>
       </c>
       <c r="BQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
         <v>0</v>
       </c>
       <c r="BU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BW16" t="n">
-        <v>-0.08402373015047923</v>
+        <v>-0.1542162058741393</v>
       </c>
       <c r="BX16" t="n">
-        <v>0.1206688143755325</v>
+        <v>0.4364260864209127</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.1415011688414384</v>
+        <v>0.01811246512496946</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
       </c>
       <c r="CB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC16" t="n">
         <v>0</v>
       </c>
       <c r="CD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE16" t="n">
         <v>0</v>
       </c>
       <c r="CF16" t="n">
-        <v>0.08658891207835391</v>
+        <v>0.1028500904754892</v>
       </c>
       <c r="CG16" t="n">
-        <v>-0.06764746524567751</v>
+        <v>-0.045203591718489</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.01470984734035716</v>
+        <v>0.006544745999952469</v>
       </c>
       <c r="CI16" t="n">
         <v>-0</v>
       </c>
       <c r="CJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK16" t="n">
         <v>-0</v>
       </c>
       <c r="CL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CO16" t="n">
-        <v>0.02490211657520711</v>
+        <v>0.0133941553400648</v>
       </c>
       <c r="CP16" t="n">
-        <v>0.02839401001466998</v>
+        <v>0.006605245684622734</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.1187040221238335</v>
+        <v>0.1332083618007734</v>
       </c>
       <c r="CR16" t="n">
         <v>0</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
         <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
         <v>-0</v>
       </c>
       <c r="CX16" t="n">
-        <v>0.05017740151562487</v>
+        <v>0.08187437712283734</v>
       </c>
       <c r="CY16" t="n">
-        <v>-0.04981610299472441</v>
+        <v>-0.04960946903676532</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.02708667523864162</v>
+        <v>0.01995643703270043</v>
       </c>
       <c r="DA16" t="n">
         <v>0</v>
       </c>
       <c r="DB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DC16" t="n">
         <v>0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DG16" t="n">
-        <v>0.00507602064158093</v>
+        <v>0.02716557813875384</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0.01643737241567117</v>
+        <v>-0.1036013828707669</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.0003624386666122486</v>
+        <v>-0.02168479129837757</v>
       </c>
       <c r="DJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK16" t="n">
         <v>0</v>
@@ -9316,19 +9316,19 @@
         <v>-0</v>
       </c>
       <c r="DN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO16" t="n">
         <v>0</v>
       </c>
       <c r="DP16" t="n">
-        <v>0.07406643904780739</v>
+        <v>0.0153393464621035</v>
       </c>
       <c r="DQ16" t="n">
-        <v>0.006575690784338065</v>
+        <v>-0.03460748948582184</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.02620692795113115</v>
+        <v>0.06607605829707035</v>
       </c>
       <c r="DS16" t="n">
         <v>-0</v>
@@ -9346,25 +9346,25 @@
         <v>0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DY16" t="n">
-        <v>-0.007613804019035642</v>
+        <v>0.03969004395148817</v>
       </c>
       <c r="DZ16" t="n">
-        <v>0.02741922008532682</v>
+        <v>0.009761588983722296</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.03913118805736553</v>
+        <v>-0.1804625869629528</v>
       </c>
       <c r="EB16" t="n">
         <v>0</v>
       </c>
       <c r="EC16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE16" t="n">
         <v>0</v>
@@ -9376,22 +9376,22 @@
         <v>0</v>
       </c>
       <c r="EH16" t="n">
-        <v>0.09631655932198212</v>
+        <v>0.0695285404264831</v>
       </c>
       <c r="EI16" t="n">
-        <v>-0.1122109280043312</v>
+        <v>0.06410230011021258</v>
       </c>
       <c r="EJ16" t="n">
-        <v>-0.008785885749687188</v>
+        <v>-0.05897374309824746</v>
       </c>
       <c r="EK16" t="n">
         <v>0</v>
       </c>
       <c r="EL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN16" t="n">
         <v>0</v>
@@ -9400,55 +9400,55 @@
         <v>0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0.04695420806609359</v>
+        <v>0.03907311274802097</v>
       </c>
       <c r="ER16" t="n">
-        <v>-0.03251411459620747</v>
+        <v>-0.1053569272590499</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.02454253040138296</v>
+        <v>-0.05816920255760021</v>
       </c>
       <c r="ET16" t="n">
         <v>-0</v>
       </c>
       <c r="EU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV16" t="n">
         <v>-0</v>
       </c>
       <c r="EW16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY16" t="n">
         <v>0</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0.0635276986164332</v>
+        <v>0.09468832037608342</v>
       </c>
       <c r="FA16" t="n">
-        <v>-0.05302577552943145</v>
+        <v>-0.08671646883917458</v>
       </c>
       <c r="FB16" t="n">
-        <v>-0.0173531347865908</v>
+        <v>0.01548837558284901</v>
       </c>
       <c r="FC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FE16" t="n">
         <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>-0</v>
@@ -9457,19 +9457,19 @@
         <v>0</v>
       </c>
       <c r="FI16" t="n">
-        <v>-0.007160722443319895</v>
+        <v>0.1628715017012778</v>
       </c>
       <c r="FJ16" t="n">
-        <v>0.05030517038087441</v>
+        <v>-0.1063279642336034</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.04377788997541498</v>
+        <v>-0.1403881559825494</v>
       </c>
       <c r="FL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN16" t="n">
         <v>-0</v>
@@ -9478,55 +9478,55 @@
         <v>0</v>
       </c>
       <c r="FP16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FR16" t="n">
-        <v>0.02103410452813839</v>
+        <v>0.00677583426957004</v>
       </c>
       <c r="FS16" t="n">
-        <v>0.01027163786745371</v>
+        <v>0.009239795965432718</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.03011828579788457</v>
+        <v>-0.02631896709030042</v>
       </c>
       <c r="FU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV16" t="n">
         <v>0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
         <v>0</v>
       </c>
       <c r="FY16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GA16" t="n">
-        <v>0.08161979285506925</v>
+        <v>0.07163612235830812</v>
       </c>
       <c r="GB16" t="n">
-        <v>0.04892921563788508</v>
+        <v>-0.1151124348045461</v>
       </c>
       <c r="GC16" t="n">
         <v>0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
       </c>
       <c r="GF16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG16" t="n">
         <v>0</v>
